--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ignacio Pardo\Desktop\buscador_precios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F4A995-CDD4-4319-8E01-2A7B455379B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DC76E1-3B98-4F7C-B064-D6509B86E8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2445" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -282,8 +282,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -1386,7 +1387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1403</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1404</v>
       </c>
@@ -1420,7 +1421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1408</v>
       </c>
@@ -1437,7 +1438,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1410</v>
       </c>
@@ -1454,7 +1455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1454</v>
       </c>
@@ -1471,7 +1472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1456</v>
       </c>
@@ -1488,7 +1489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1458</v>
       </c>
@@ -1505,7 +1506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1460</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1461</v>
       </c>
@@ -1539,7 +1540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1462</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1463</v>
       </c>
@@ -1573,7 +1574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1466</v>
       </c>
@@ -1587,10 +1588,10 @@
         <v>123456</v>
       </c>
       <c r="E60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1468</v>
       </c>
@@ -1607,7 +1608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1472</v>
       </c>
@@ -1624,7 +1625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1507</v>
       </c>
@@ -1641,7 +1642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1525</v>
       </c>
@@ -1657,6 +1658,7 @@
       <c r="E64">
         <v>4</v>
       </c>
+      <c r="I64" s="1"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ignacio Pardo\Desktop\buscador_precios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DC76E1-3B98-4F7C-B064-D6509B86E8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB81FAE7-1985-4B1D-951F-D8268E2973C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2445" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="75">
   <si>
     <t>N_CLIENTE</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>TIEMPO</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
   </si>
 </sst>
 </file>
@@ -282,9 +285,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -1387,7 +1389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1403</v>
       </c>
@@ -1404,7 +1406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1404</v>
       </c>
@@ -1421,7 +1423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1408</v>
       </c>
@@ -1438,7 +1440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1410</v>
       </c>
@@ -1455,7 +1457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1454</v>
       </c>
@@ -1472,7 +1474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1456</v>
       </c>
@@ -1489,7 +1491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1458</v>
       </c>
@@ -1506,7 +1508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1460</v>
       </c>
@@ -1523,7 +1525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1461</v>
       </c>
@@ -1540,7 +1542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1462</v>
       </c>
@@ -1557,7 +1559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1463</v>
       </c>
@@ -1574,7 +1576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1466</v>
       </c>
@@ -1591,7 +1593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1468</v>
       </c>
@@ -1608,7 +1610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1472</v>
       </c>
@@ -1625,7 +1627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1507</v>
       </c>
@@ -1642,7 +1644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1525</v>
       </c>
@@ -1658,7 +1660,6 @@
       <c r="E64">
         <v>4</v>
       </c>
-      <c r="I64" s="1"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
@@ -1708,7 +1709,24 @@
         <v>123456</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1726</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68">
+        <v>123456</v>
+      </c>
+      <c r="E68">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
